--- a/template/dc_char_position.xlsx
+++ b/template/dc_char_position.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,12 +27,7 @@
     </font>
     <font>
       <name val="MS Pゴシック"/>
-      <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="MS Pゴシック"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -44,12 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4E6F1"/>
-        <bgColor rgb="00D4E6F1"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -63,18 +58,57 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,584 +474,560 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ﾕﾆｯﾄ No.</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ﾕﾆｯﾄNo.</t>
+          <t>極</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>部</t>
+          <t>入力ｺｰﾄﾞ</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>入力ｺｰﾄﾞ</t>
+          <t>測定電圧(V)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>出力電圧 (V)</t>
+          <t>許容誤差(V)(&lt;0.1%)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>期待値±誤差 (V)</t>
+          <t>誤差(V)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>誤差 (V)</t>
+          <t>誤差(%)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>誤差(%)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1PB397MK2
+DEF0</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1PB397MK2</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
           <t>POS</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>FFFFF H</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>160.000±0.160</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>DEF0</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>80000 H</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>0.000±0.100</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>00000 H</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>-160.000±0.160</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>00000 H</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>160.000±0.160</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>80000 H</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>0.000±0.100</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>FFFFF H</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>-160.000±0.160</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1PB397MK2
+DEF1</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1PB397MK2</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
           <t>POS</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>FFFFF H</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>160.000±0.160</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>DEF1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>80000 H</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>0.000±0.100</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>00000 H</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>-160.000±0.160</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>00000 H</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>160.000±0.160</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>80000 H</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>0.000±0.100</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>FFFFF H</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>-160.000±0.160</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1PB397MK2
+DEF2</t>
+        </is>
+      </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1PB397MK2</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
           <t>POS</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>FFFFF H</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>160.000±0.160</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>DEF2</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr">
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>80000 H</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>0.000±0.100</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>00000 H</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>-160.000±0.160</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>00000 H</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>160.000±0.160</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>80000 H</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>0.000±0.100</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>FFFFF H</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>-160.000±0.160</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>1PB397MK2
+DEF3</t>
+        </is>
+      </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1PB397MK2</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
           <t>POS</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>FFFFF H</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>160.000±0.160</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>DEF3</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr">
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>80000 H</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>0.000±0.100</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>00000 H</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>-160.000±0.160</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>00000 H</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>160.000±0.160</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>80000 H</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>0.000±0.100</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>FFFFF H</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>-160.000±0.160</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="1" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B5:B7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/template/dc_char_position.xlsx
+++ b/template/dc_char_position.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POSTION" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="moni" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1030,4 +1031,424 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ﾕﾆｯﾄ No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>極</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>入力ｺｰﾄﾞ</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>測定電圧(V)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>許容誤差(V)(&lt;1%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>誤差(V)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>誤差(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1PB397MK2
+DEF0</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>FFFFF H</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>+5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>00000 H</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>-5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>00000 H</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>FFFFF H</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>-5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1PB397MK2
+DEF1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>FFFFF H</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>+5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>00000 H</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>00000 H</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>FFFFF H</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1PB397MK2
+DEF2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>FFFFF H</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>00000 H</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>00000 H</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>FFFFF H</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1PB397MK2
+DEF3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>FFFFF H</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>00000 H</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>00000 H</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>FFFFF H</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-5.00±0.05</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A10:A13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>